--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/190.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/190.xlsx
@@ -426,13 +426,13 @@
         <v>6.218279297115029</v>
       </c>
       <c r="E2">
-        <v>-14.64180387385798</v>
+        <v>-13.92346109896924</v>
       </c>
       <c r="F2">
-        <v>-3.043071585721507</v>
+        <v>-3.522871097464412</v>
       </c>
       <c r="G2">
-        <v>-7.160466171742005</v>
+        <v>-6.306719514255977</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.05695099282083</v>
       </c>
       <c r="E3">
-        <v>-13.8816361130344</v>
+        <v>-13.87828051379472</v>
       </c>
       <c r="F3">
-        <v>-3.405213933407784</v>
+        <v>-3.537840524800401</v>
       </c>
       <c r="G3">
-        <v>-7.147396137952962</v>
+        <v>-6.753944421701661</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.792791704215258</v>
       </c>
       <c r="E4">
-        <v>-14.63040117630666</v>
+        <v>-14.24606958727568</v>
       </c>
       <c r="F4">
-        <v>-3.344014149688956</v>
+        <v>-3.480768495849724</v>
       </c>
       <c r="G4">
-        <v>-6.842405509056526</v>
+        <v>-5.68626037983131</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.448355702782187</v>
       </c>
       <c r="E5">
-        <v>-16.1805974555604</v>
+        <v>-15.78400728739065</v>
       </c>
       <c r="F5">
-        <v>-3.670492795582506</v>
+        <v>-3.532794110582547</v>
       </c>
       <c r="G5">
-        <v>-6.492242486276735</v>
+        <v>-5.586857939469153</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.040106184701671</v>
       </c>
       <c r="E6">
-        <v>-15.12520941722877</v>
+        <v>-15.6624177602847</v>
       </c>
       <c r="F6">
-        <v>-3.868952229577808</v>
+        <v>-3.434137209643931</v>
       </c>
       <c r="G6">
-        <v>-6.740470501356827</v>
+        <v>-5.652870217522221</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.596131687128664</v>
       </c>
       <c r="E7">
-        <v>-16.34460519869619</v>
+        <v>-17.0837744255462</v>
       </c>
       <c r="F7">
-        <v>-3.725950336465127</v>
+        <v>-3.155103306745723</v>
       </c>
       <c r="G7">
-        <v>-6.337315576129921</v>
+        <v>-4.732101565593648</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.15031304899449</v>
       </c>
       <c r="E8">
-        <v>-17.24143324812325</v>
+        <v>-16.89607370640227</v>
       </c>
       <c r="F8">
-        <v>-3.819390179500911</v>
+        <v>-3.62394351774959</v>
       </c>
       <c r="G8">
-        <v>-6.07963264298967</v>
+        <v>-5.201374706330877</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.736024383592535</v>
       </c>
       <c r="E9">
-        <v>-17.45476513015059</v>
+        <v>-17.2874561294632</v>
       </c>
       <c r="F9">
-        <v>-3.74615504578681</v>
+        <v>-3.805244149363304</v>
       </c>
       <c r="G9">
-        <v>-6.835320941602486</v>
+        <v>-4.606827211842086</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.383652507898756</v>
       </c>
       <c r="E10">
-        <v>-16.58621740090144</v>
+        <v>-17.81881368410122</v>
       </c>
       <c r="F10">
-        <v>-3.836695602912796</v>
+        <v>-3.985186258436427</v>
       </c>
       <c r="G10">
-        <v>-5.82753128962863</v>
+        <v>-4.066443552921311</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.122912532598516</v>
       </c>
       <c r="E11">
-        <v>-18.0657015585254</v>
+        <v>-18.14648953482224</v>
       </c>
       <c r="F11">
-        <v>-4.014140184266478</v>
+        <v>-3.617966846938392</v>
       </c>
       <c r="G11">
-        <v>-4.948899261323899</v>
+        <v>-4.051069379436936</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.968567739438514</v>
       </c>
       <c r="E12">
-        <v>-18.56544130764186</v>
+        <v>-18.83969475049439</v>
       </c>
       <c r="F12">
-        <v>-3.623390996691923</v>
+        <v>-4.008775676965948</v>
       </c>
       <c r="G12">
-        <v>-5.182272858569283</v>
+        <v>-3.91518803777755</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.923579810504401</v>
       </c>
       <c r="E13">
-        <v>-19.0994117917823</v>
+        <v>-19.45876884666098</v>
       </c>
       <c r="F13">
-        <v>-3.658671992744557</v>
+        <v>-3.911643800415887</v>
       </c>
       <c r="G13">
-        <v>-3.766938497983447</v>
+        <v>-3.408644775359205</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.985058164870374</v>
       </c>
       <c r="E14">
-        <v>-20.69663627360569</v>
+        <v>-19.76819041865708</v>
       </c>
       <c r="F14">
-        <v>-4.169645454957015</v>
+        <v>-3.57863844775568</v>
       </c>
       <c r="G14">
-        <v>-4.19663406679869</v>
+        <v>-3.649976924080996</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.135505808030945</v>
       </c>
       <c r="E15">
-        <v>-20.99371322545688</v>
+        <v>-19.9970957227968</v>
       </c>
       <c r="F15">
-        <v>-3.649190499452114</v>
+        <v>-3.889296932990565</v>
       </c>
       <c r="G15">
-        <v>-4.208244150004914</v>
+        <v>-2.63160014747255</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.351883037610483</v>
       </c>
       <c r="E16">
-        <v>-21.51705538110132</v>
+        <v>-21.41737913971849</v>
       </c>
       <c r="F16">
-        <v>-3.408324453005296</v>
+        <v>-3.509806086787458</v>
       </c>
       <c r="G16">
-        <v>-3.165180635310123</v>
+        <v>-1.755202737406828</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.611579987161914</v>
       </c>
       <c r="E17">
-        <v>-22.08321878696229</v>
+        <v>-21.68942268725528</v>
       </c>
       <c r="F17">
-        <v>-3.531256660682951</v>
+        <v>-3.560169996510265</v>
       </c>
       <c r="G17">
-        <v>-2.543244997574941</v>
+        <v>-1.582206869706673</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.886286875427083</v>
       </c>
       <c r="E18">
-        <v>-22.63312044266172</v>
+        <v>-23.45550037940267</v>
       </c>
       <c r="F18">
-        <v>-2.928275602674149</v>
+        <v>-3.395033298027378</v>
       </c>
       <c r="G18">
-        <v>-1.887114734964628</v>
+        <v>-1.896162455923456</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.150438771715905</v>
       </c>
       <c r="E19">
-        <v>-23.35224664355378</v>
+        <v>-22.26003758306579</v>
       </c>
       <c r="F19">
-        <v>-3.159390936422614</v>
+        <v>-3.257204559345179</v>
       </c>
       <c r="G19">
-        <v>-3.177601802173469</v>
+        <v>-1.570341874493925</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.383978789187382</v>
       </c>
       <c r="E20">
-        <v>-24.44164805015701</v>
+        <v>-23.6684699835094</v>
       </c>
       <c r="F20">
-        <v>-3.16212703395406</v>
+        <v>-2.959208498229488</v>
       </c>
       <c r="G20">
-        <v>-1.775867162662959</v>
+        <v>-1.300386749039596</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.566706041042106</v>
       </c>
       <c r="E21">
-        <v>-24.04436049699009</v>
+        <v>-24.0199882498808</v>
       </c>
       <c r="F21">
-        <v>-2.512233044822514</v>
+        <v>-2.808853187682155</v>
       </c>
       <c r="G21">
-        <v>-1.839793797026286</v>
+        <v>-1.676282642296142</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.683141637421394</v>
       </c>
       <c r="E22">
-        <v>-24.66755097602965</v>
+        <v>-25.05201841928086</v>
       </c>
       <c r="F22">
-        <v>-2.436258500107355</v>
+        <v>-2.594171006470427</v>
       </c>
       <c r="G22">
-        <v>-1.850771566034509</v>
+        <v>-1.146691361833391</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.724117948928844</v>
       </c>
       <c r="E23">
-        <v>-24.85964884343502</v>
+        <v>-24.44505799108479</v>
       </c>
       <c r="F23">
-        <v>-2.645248140527045</v>
+        <v>-2.348660303996112</v>
       </c>
       <c r="G23">
-        <v>-2.338537414154108</v>
+        <v>-0.3234282076729718</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.682949526604308</v>
       </c>
       <c r="E24">
-        <v>-25.68244992825869</v>
+        <v>-24.57512935000711</v>
       </c>
       <c r="F24">
-        <v>-2.097616107271097</v>
+        <v>-2.311017632478097</v>
       </c>
       <c r="G24">
-        <v>-1.232126610565363</v>
+        <v>-0.9947174583076082</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.558371612480948</v>
       </c>
       <c r="E25">
-        <v>-26.36726841006864</v>
+        <v>-26.05924160806691</v>
       </c>
       <c r="F25">
-        <v>-2.501541306754581</v>
+        <v>-2.451251121730623</v>
       </c>
       <c r="G25">
-        <v>-1.87969911295666</v>
+        <v>-0.9200348614871895</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.356501497893237</v>
       </c>
       <c r="E26">
-        <v>-27.6758343732211</v>
+        <v>-26.32634459046132</v>
       </c>
       <c r="F26">
-        <v>-2.205404102090772</v>
+        <v>-2.467340501795197</v>
       </c>
       <c r="G26">
-        <v>-1.176347228774183</v>
+        <v>-1.747767252125625</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.086269024675621</v>
       </c>
       <c r="E27">
-        <v>-25.74700785371204</v>
+        <v>-25.79637274886965</v>
       </c>
       <c r="F27">
-        <v>-2.51735981067844</v>
+        <v>-2.07851975353436</v>
       </c>
       <c r="G27">
-        <v>-3.466430347747183</v>
+        <v>-1.282950105684254</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.760419773759501</v>
       </c>
       <c r="E28">
-        <v>-26.11587470400683</v>
+        <v>-24.5392321365483</v>
       </c>
       <c r="F28">
-        <v>-2.04876148295619</v>
+        <v>-2.521840449960183</v>
       </c>
       <c r="G28">
-        <v>-2.48211246364676</v>
+        <v>-1.88010962060353</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.397948210872575</v>
       </c>
       <c r="E29">
-        <v>-25.63737349798634</v>
+        <v>-25.1784986983151</v>
       </c>
       <c r="F29">
-        <v>-2.366815632363269</v>
+        <v>-2.202272044940786</v>
       </c>
       <c r="G29">
-        <v>-1.998991310918758</v>
+        <v>-1.782554464652287</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.017514540703556</v>
       </c>
       <c r="E30">
-        <v>-27.21503044362259</v>
+        <v>-24.4885766262985</v>
       </c>
       <c r="F30">
-        <v>-1.892283708934767</v>
+        <v>-2.491715212622573</v>
       </c>
       <c r="G30">
-        <v>-2.23554965297292</v>
+        <v>-2.357510150639671</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.637591811511266</v>
       </c>
       <c r="E31">
-        <v>-25.97525652912065</v>
+        <v>-24.13668249658446</v>
       </c>
       <c r="F31">
-        <v>-1.627636062720978</v>
+        <v>-2.191043524795839</v>
       </c>
       <c r="G31">
-        <v>-2.740669380809379</v>
+        <v>-2.220638955864043</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.280096026652403</v>
       </c>
       <c r="E32">
-        <v>-26.53355850410431</v>
+        <v>-24.43842830513756</v>
       </c>
       <c r="F32">
-        <v>-2.142270080486407</v>
+        <v>-1.936723963360155</v>
       </c>
       <c r="G32">
-        <v>-2.813723189224476</v>
+        <v>-1.860103993909714</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.96243529558059</v>
       </c>
       <c r="E33">
-        <v>-24.64197415483433</v>
+        <v>-24.43704259209121</v>
       </c>
       <c r="F33">
-        <v>-2.081859730902448</v>
+        <v>-2.090351325148545</v>
       </c>
       <c r="G33">
-        <v>-1.644577547666542</v>
+        <v>-2.359592483783873</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.697579711585494</v>
       </c>
       <c r="E34">
-        <v>-24.43446136190684</v>
+        <v>-23.69295997094288</v>
       </c>
       <c r="F34">
-        <v>-2.050765303703562</v>
+        <v>-2.252905174069503</v>
       </c>
       <c r="G34">
-        <v>-2.500413159387851</v>
+        <v>-2.450241841740196</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.497388861191447</v>
       </c>
       <c r="E35">
-        <v>-25.10445361981568</v>
+        <v>-23.55725519035503</v>
       </c>
       <c r="F35">
-        <v>-1.571380804029461</v>
+        <v>-2.06948889210904</v>
       </c>
       <c r="G35">
-        <v>-3.170027273979616</v>
+        <v>-2.1426160185945</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.3657734844384</v>
       </c>
       <c r="E36">
-        <v>-24.30210312361065</v>
+        <v>-22.81561794517084</v>
       </c>
       <c r="F36">
-        <v>-1.660221551244902</v>
+        <v>-2.109147809885469</v>
       </c>
       <c r="G36">
-        <v>-2.441127909870583</v>
+        <v>-2.774251554759746</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.300730862049989</v>
       </c>
       <c r="E37">
-        <v>-23.97267928192267</v>
+        <v>-23.34199870687442</v>
       </c>
       <c r="F37">
-        <v>-1.714543400418285</v>
+        <v>-1.921516794579561</v>
       </c>
       <c r="G37">
-        <v>-3.631222683601024</v>
+        <v>-2.544042839049906</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.298278067999321</v>
       </c>
       <c r="E38">
-        <v>-23.55749067100342</v>
+        <v>-22.04379389225151</v>
       </c>
       <c r="F38">
-        <v>-1.065269858471436</v>
+        <v>-1.695630115877567</v>
       </c>
       <c r="G38">
-        <v>-2.641131208080112</v>
+        <v>-2.446322155821699</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.34901006033353</v>
       </c>
       <c r="E39">
-        <v>-22.12671477980597</v>
+        <v>-21.6448036328577</v>
       </c>
       <c r="F39">
-        <v>-1.842833488457247</v>
+        <v>-1.501768949335204</v>
       </c>
       <c r="G39">
-        <v>-3.267638709205027</v>
+        <v>-1.495665898764585</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.442238660715939</v>
       </c>
       <c r="E40">
-        <v>-22.20128063281626</v>
+        <v>-21.78998198106961</v>
       </c>
       <c r="F40">
-        <v>-2.14971876017238</v>
+        <v>-1.913481630772406</v>
       </c>
       <c r="G40">
-        <v>-3.127324547068557</v>
+        <v>-2.484092169879244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.56743527691838</v>
       </c>
       <c r="E41">
-        <v>-20.41208508085971</v>
+        <v>-20.58536261028921</v>
       </c>
       <c r="F41">
-        <v>-1.396889352466759</v>
+        <v>-1.696810539426556</v>
       </c>
       <c r="G41">
-        <v>-2.755480761552078</v>
+        <v>-2.105246580547206</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.711263480303465</v>
       </c>
       <c r="E42">
-        <v>-22.30993683815631</v>
+        <v>-19.51334601540142</v>
       </c>
       <c r="F42">
-        <v>-1.989666580807877</v>
+        <v>-1.791398499682621</v>
       </c>
       <c r="G42">
-        <v>-2.647917826435618</v>
+        <v>-2.534965323181224</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.861051264792714</v>
       </c>
       <c r="E43">
-        <v>-20.96624350212635</v>
+        <v>-20.63271686298742</v>
       </c>
       <c r="F43">
-        <v>-1.733542835168895</v>
+        <v>-1.65300398606431</v>
       </c>
       <c r="G43">
-        <v>-3.308937764807435</v>
+        <v>-2.538871766917564</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.004566139838117</v>
       </c>
       <c r="E44">
-        <v>-20.61831178716902</v>
+        <v>-19.96543716100918</v>
       </c>
       <c r="F44">
-        <v>-1.587575386754191</v>
+        <v>-1.706914965005905</v>
       </c>
       <c r="G44">
-        <v>-2.907405006894772</v>
+        <v>-1.827455393801422</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.129293712707275</v>
       </c>
       <c r="E45">
-        <v>-19.86347856872648</v>
+        <v>-18.95568255525285</v>
       </c>
       <c r="F45">
-        <v>-1.673859792164593</v>
+        <v>-1.629236468543187</v>
       </c>
       <c r="G45">
-        <v>-2.346088768529185</v>
+        <v>-2.896844366624497</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.225191075331292</v>
       </c>
       <c r="E46">
-        <v>-18.75616704742291</v>
+        <v>-17.88553622013023</v>
       </c>
       <c r="F46">
-        <v>-1.372633098177984</v>
+        <v>-1.795300110149806</v>
       </c>
       <c r="G46">
-        <v>-3.114287618734907</v>
+        <v>-1.875094144111534</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.28464905406953</v>
       </c>
       <c r="E47">
-        <v>-17.51236279105415</v>
+        <v>-18.42092864510908</v>
       </c>
       <c r="F47">
-        <v>-1.582889312356554</v>
+        <v>-2.062902542889381</v>
       </c>
       <c r="G47">
-        <v>-2.763293649024758</v>
+        <v>-2.595783355283175</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.302610329812597</v>
       </c>
       <c r="E48">
-        <v>-17.30171176563935</v>
+        <v>-18.05860091128137</v>
       </c>
       <c r="F48">
-        <v>-1.174993747911453</v>
+        <v>-1.948535654156673</v>
       </c>
       <c r="G48">
-        <v>-3.531025712309443</v>
+        <v>-2.340368145837325</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.276985195416101</v>
       </c>
       <c r="E49">
-        <v>-18.27900174123469</v>
+        <v>-17.70906611652532</v>
       </c>
       <c r="F49">
-        <v>-1.620550207957431</v>
+        <v>-1.632773597353141</v>
       </c>
       <c r="G49">
-        <v>-3.02728648196286</v>
+        <v>-2.23891316724082</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.208207194638479</v>
       </c>
       <c r="E50">
-        <v>-15.6662533777692</v>
+        <v>-16.08764146960495</v>
       </c>
       <c r="F50">
-        <v>-1.15727745426778</v>
+        <v>-1.595446533815592</v>
       </c>
       <c r="G50">
-        <v>-3.897685183511423</v>
+        <v>-2.172165948078034</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.099514627227293</v>
       </c>
       <c r="E51">
-        <v>-17.25870937646251</v>
+        <v>-16.93189846427695</v>
       </c>
       <c r="F51">
-        <v>-1.822801079555347</v>
+        <v>-2.005257283695966</v>
       </c>
       <c r="G51">
-        <v>-3.744651905413073</v>
+        <v>-3.153242808095511</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.955010964945583</v>
       </c>
       <c r="E52">
-        <v>-15.93845542189625</v>
+        <v>-15.78863991630049</v>
       </c>
       <c r="F52">
-        <v>-1.343689112756766</v>
+        <v>-1.685046893939401</v>
       </c>
       <c r="G52">
-        <v>-3.520167122940633</v>
+        <v>-2.549902504654416</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.780047589017926</v>
       </c>
       <c r="E53">
-        <v>-14.37784365242488</v>
+        <v>-14.77144955622357</v>
       </c>
       <c r="F53">
-        <v>-1.243272759454604</v>
+        <v>-1.902340917572156</v>
       </c>
       <c r="G53">
-        <v>-3.472823011183516</v>
+        <v>-2.576764271160062</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.58238816658573</v>
       </c>
       <c r="E54">
-        <v>-15.90616287374756</v>
+        <v>-15.4049513705786</v>
       </c>
       <c r="F54">
-        <v>-1.409506216378798</v>
+        <v>-1.877677106521203</v>
       </c>
       <c r="G54">
-        <v>-4.23615204890097</v>
+        <v>-2.290044543094863</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.368134368021344</v>
       </c>
       <c r="E55">
-        <v>-14.71406473359837</v>
+        <v>-15.63563636500334</v>
       </c>
       <c r="F55">
-        <v>-1.477656002607113</v>
+        <v>-1.59374755227245</v>
       </c>
       <c r="G55">
-        <v>-3.647311934921882</v>
+        <v>-3.546234358516855</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.142617944135036</v>
       </c>
       <c r="E56">
-        <v>-14.40930296135616</v>
+        <v>-14.85393118179928</v>
       </c>
       <c r="F56">
-        <v>-1.335011135845038</v>
+        <v>-1.855893528929784</v>
       </c>
       <c r="G56">
-        <v>-4.866986433045713</v>
+        <v>-3.351693460447123</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9133301650531855</v>
       </c>
       <c r="E57">
-        <v>-14.45843690433939</v>
+        <v>-13.97287127886693</v>
       </c>
       <c r="F57">
-        <v>-1.370902638673536</v>
+        <v>-1.750327215484418</v>
       </c>
       <c r="G57">
-        <v>-4.95511646584665</v>
+        <v>-3.691272669137864</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.6841008344810151</v>
       </c>
       <c r="E58">
-        <v>-13.23033739582923</v>
+        <v>-14.96455727333266</v>
       </c>
       <c r="F58">
-        <v>-1.723961109420713</v>
+        <v>-1.821603260290899</v>
       </c>
       <c r="G58">
-        <v>-3.992039041926191</v>
+        <v>-2.979356403645292</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.4565503239182525</v>
       </c>
       <c r="E59">
-        <v>-13.40445269295014</v>
+        <v>-13.28250541639759</v>
       </c>
       <c r="F59">
-        <v>-1.538620529983546</v>
+        <v>-1.835538885108195</v>
       </c>
       <c r="G59">
-        <v>-3.970186130821462</v>
+        <v>-3.297172085960865</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2347419406123413</v>
       </c>
       <c r="E60">
-        <v>-12.60247806008775</v>
+        <v>-14.81637201837966</v>
       </c>
       <c r="F60">
-        <v>-1.439027573879767</v>
+        <v>-1.908403738593245</v>
       </c>
       <c r="G60">
-        <v>-4.711430519246438</v>
+        <v>-3.408654706995823</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.0186618752028351</v>
       </c>
       <c r="E61">
-        <v>-13.88844693794194</v>
+        <v>-13.95553175189156</v>
       </c>
       <c r="F61">
-        <v>-1.503144867591254</v>
+        <v>-1.675574512688388</v>
       </c>
       <c r="G61">
-        <v>-3.627365898047774</v>
+        <v>-3.958516457795531</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.1940913102527702</v>
       </c>
       <c r="E62">
-        <v>-13.75255648991976</v>
+        <v>-13.39529611850663</v>
       </c>
       <c r="F62">
-        <v>-0.9395874710164862</v>
+        <v>-1.777253297912416</v>
       </c>
       <c r="G62">
-        <v>-4.700230943687083</v>
+        <v>-3.861484368039493</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.4021662825434774</v>
       </c>
       <c r="E63">
-        <v>-14.09525781739823</v>
+        <v>-12.7100112038739</v>
       </c>
       <c r="F63">
-        <v>-1.275862389815543</v>
+        <v>-1.412044334100976</v>
       </c>
       <c r="G63">
-        <v>-4.421694884194963</v>
+        <v>-3.843849091951795</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.6070828265531095</v>
       </c>
       <c r="E64">
-        <v>-12.75938515597952</v>
+        <v>-12.90604884366594</v>
       </c>
       <c r="F64">
-        <v>-1.314073321371878</v>
+        <v>-1.904561770579061</v>
       </c>
       <c r="G64">
-        <v>-4.10941774456659</v>
+        <v>-3.719299747673334</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.8119929652196918</v>
       </c>
       <c r="E65">
-        <v>-12.5255211728014</v>
+        <v>-12.7924883009756</v>
       </c>
       <c r="F65">
-        <v>-1.682681076637005</v>
+        <v>-1.4380608691207</v>
       </c>
       <c r="G65">
-        <v>-5.279142731593897</v>
+        <v>-3.775890213121636</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.015387831476927</v>
       </c>
       <c r="E66">
-        <v>-13.25806071370418</v>
+        <v>-13.04209325980438</v>
       </c>
       <c r="F66">
-        <v>-1.966536906186909</v>
+        <v>-1.640276120920296</v>
       </c>
       <c r="G66">
-        <v>-5.270773672470619</v>
+        <v>-3.472640931178856</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.216870706547885</v>
       </c>
       <c r="E67">
-        <v>-12.5532671330464</v>
+        <v>-12.61856772823701</v>
       </c>
       <c r="F67">
-        <v>-1.544382653637419</v>
+        <v>-2.031745988135286</v>
       </c>
       <c r="G67">
-        <v>-4.459494693162362</v>
+        <v>-3.734323003330547</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.416911884325468</v>
       </c>
       <c r="E68">
-        <v>-12.47605212274161</v>
+        <v>-12.17840911163946</v>
       </c>
       <c r="F68">
-        <v>-1.589311644830459</v>
+        <v>-2.202898290697303</v>
       </c>
       <c r="G68">
-        <v>-4.896403940707676</v>
+        <v>-3.867906826385679</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.611880625157698</v>
       </c>
       <c r="E69">
-        <v>-12.67820320244402</v>
+        <v>-12.31307687167956</v>
       </c>
       <c r="F69">
-        <v>-1.838667628788569</v>
+        <v>-1.673137455789352</v>
       </c>
       <c r="G69">
-        <v>-4.916588336860612</v>
+        <v>-3.178810151295302</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.797777450750677</v>
       </c>
       <c r="E70">
-        <v>-12.58265692935618</v>
+        <v>-13.50601730799417</v>
       </c>
       <c r="F70">
-        <v>-1.631933632806702</v>
+        <v>-2.020069321225424</v>
       </c>
       <c r="G70">
-        <v>-5.70447831193392</v>
+        <v>-3.945453045097567</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.971683567686775</v>
       </c>
       <c r="E71">
-        <v>-12.65737222200873</v>
+        <v>-12.74100407998239</v>
       </c>
       <c r="F71">
-        <v>-2.107009793618844</v>
+        <v>-2.070625412185681</v>
       </c>
       <c r="G71">
-        <v>-5.085224216085548</v>
+        <v>-3.922073972499234</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.128383155767707</v>
       </c>
       <c r="E72">
-        <v>-13.85455130999452</v>
+        <v>-12.16231944349021</v>
       </c>
       <c r="F72">
-        <v>-2.137321413622083</v>
+        <v>-2.319449584271193</v>
       </c>
       <c r="G72">
-        <v>-3.741467160604294</v>
+        <v>-3.881023207812271</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.262630066376159</v>
       </c>
       <c r="E73">
-        <v>-10.95805329368242</v>
+        <v>-12.66423286013035</v>
       </c>
       <c r="F73">
-        <v>-1.989451205283149</v>
+        <v>-2.551530794411323</v>
       </c>
       <c r="G73">
-        <v>-4.086790165805672</v>
+        <v>-3.654846736569264</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.370937117969929</v>
       </c>
       <c r="E74">
-        <v>-13.08662627319581</v>
+        <v>-14.27952142477034</v>
       </c>
       <c r="F74">
-        <v>-2.152610590775554</v>
+        <v>-2.694497067725683</v>
       </c>
       <c r="G74">
-        <v>-4.59408823260697</v>
+        <v>-4.010300011120811</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.44964092643733</v>
       </c>
       <c r="E75">
-        <v>-13.87492038608102</v>
+        <v>-13.91765559529141</v>
       </c>
       <c r="F75">
-        <v>-2.238271235531648</v>
+        <v>-2.357358161725507</v>
       </c>
       <c r="G75">
-        <v>-4.353848563913139</v>
+        <v>-3.560635231612684</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.495170081409786</v>
       </c>
       <c r="E76">
-        <v>-13.69431578570711</v>
+        <v>-13.59599355805258</v>
       </c>
       <c r="F76">
-        <v>-2.301867486146774</v>
+        <v>-2.752534973068026</v>
       </c>
       <c r="G76">
-        <v>-5.320905263571802</v>
+        <v>-3.662302085123702</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.505441768984107</v>
       </c>
       <c r="E77">
-        <v>-14.60217519781685</v>
+        <v>-14.34144830682523</v>
       </c>
       <c r="F77">
-        <v>-2.45460269624235</v>
+        <v>-2.679742187547019</v>
       </c>
       <c r="G77">
-        <v>-3.391012809817046</v>
+        <v>-3.829544224676604</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.479337230208587</v>
       </c>
       <c r="E78">
-        <v>-14.02166105782558</v>
+        <v>-15.21716913890253</v>
       </c>
       <c r="F78">
-        <v>-1.820272902242003</v>
+        <v>-3.021203514655003</v>
       </c>
       <c r="G78">
-        <v>-4.006929875761833</v>
+        <v>-3.718223820373071</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.415882672396188</v>
       </c>
       <c r="E79">
-        <v>-15.45904852107423</v>
+        <v>-16.00568514701413</v>
       </c>
       <c r="F79">
-        <v>-2.679996496339678</v>
+        <v>-3.128727260273184</v>
       </c>
       <c r="G79">
-        <v>-3.616510619224503</v>
+        <v>-3.061653255206035</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.314779302464547</v>
       </c>
       <c r="E80">
-        <v>-15.82375370375597</v>
+        <v>-15.58438309618452</v>
       </c>
       <c r="F80">
-        <v>-2.770604979592694</v>
+        <v>-3.014707457482249</v>
       </c>
       <c r="G80">
-        <v>-4.189327692793518</v>
+        <v>-3.690557591301382</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.178176511173261</v>
       </c>
       <c r="E81">
-        <v>-16.44111150827365</v>
+        <v>-16.25255943601628</v>
       </c>
       <c r="F81">
-        <v>-2.192125372623896</v>
+        <v>-2.931338076962299</v>
       </c>
       <c r="G81">
-        <v>-3.549627667694608</v>
+        <v>-3.145267703891407</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.009322120124678</v>
       </c>
       <c r="E82">
-        <v>-16.61880882833464</v>
+        <v>-16.36559920419575</v>
       </c>
       <c r="F82">
-        <v>-2.385898732221561</v>
+        <v>-2.899152689893927</v>
       </c>
       <c r="G82">
-        <v>-4.131184581487299</v>
+        <v>-2.584434805174554</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.81155331318735</v>
       </c>
       <c r="E83">
-        <v>-17.91043829869841</v>
+        <v>-18.27202789126287</v>
       </c>
       <c r="F83">
-        <v>-2.816806343116434</v>
+        <v>-3.252877996400358</v>
       </c>
       <c r="G83">
-        <v>-3.931879808386555</v>
+        <v>-3.038714485164424</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.591197600722268</v>
       </c>
       <c r="E84">
-        <v>-19.4791469796955</v>
+        <v>-19.14846422223339</v>
       </c>
       <c r="F84">
-        <v>-2.944719523987122</v>
+        <v>-3.385007567351296</v>
       </c>
       <c r="G84">
-        <v>-3.481271523399736</v>
+        <v>-2.937411791662726</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.355242126541344</v>
       </c>
       <c r="E85">
-        <v>-19.3020927029436</v>
+        <v>-19.86668472832391</v>
       </c>
       <c r="F85">
-        <v>-3.058433659206424</v>
+        <v>-3.304858879293429</v>
       </c>
       <c r="G85">
-        <v>-3.049493621440292</v>
+        <v>-1.881622539914977</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.110185189387669</v>
       </c>
       <c r="E86">
-        <v>-20.67902503818986</v>
+        <v>-21.39517150318487</v>
       </c>
       <c r="F86">
-        <v>-3.320070189911037</v>
+        <v>-3.628689234600229</v>
       </c>
       <c r="G86">
-        <v>-3.78682163449231</v>
+        <v>-2.608932842165161</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.8659371466939905</v>
       </c>
       <c r="E87">
-        <v>-22.20717217750024</v>
+        <v>-22.49954857333147</v>
       </c>
       <c r="F87">
-        <v>-3.623728142224863</v>
+        <v>-3.820800060820476</v>
       </c>
       <c r="G87">
-        <v>-2.718485415150723</v>
+        <v>-2.761264284609185</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6327453574794792</v>
       </c>
       <c r="E88">
-        <v>-24.21849843648104</v>
+        <v>-23.73009345780578</v>
       </c>
       <c r="F88">
-        <v>-3.385218801039009</v>
+        <v>-3.278779388351093</v>
       </c>
       <c r="G88">
-        <v>-3.638833627795809</v>
+        <v>-1.869088814503296</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.4199303852767558</v>
       </c>
       <c r="E89">
-        <v>-23.56352259838164</v>
+        <v>-24.2903245627167</v>
       </c>
       <c r="F89">
-        <v>-3.199625569543989</v>
+        <v>-3.705393570997255</v>
       </c>
       <c r="G89">
-        <v>-2.45558175169504</v>
+        <v>-2.794667689100431</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2380968862593242</v>
       </c>
       <c r="E90">
-        <v>-25.29494387894833</v>
+        <v>-26.58392419201762</v>
       </c>
       <c r="F90">
-        <v>-3.111134393372529</v>
+        <v>-4.24420431978079</v>
       </c>
       <c r="G90">
-        <v>-3.31159613287547</v>
+        <v>-2.888260122041167</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.09603728909511039</v>
       </c>
       <c r="E91">
-        <v>-25.71405414835822</v>
+        <v>-26.81276609752123</v>
       </c>
       <c r="F91">
-        <v>-2.990213461748871</v>
+        <v>-4.024519627823556</v>
       </c>
       <c r="G91">
-        <v>-2.884952887047435</v>
+        <v>-2.940868001205725</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.865688888062267E-05</v>
       </c>
       <c r="E92">
-        <v>-27.82286939577615</v>
+        <v>-28.27615153004792</v>
       </c>
       <c r="F92">
-        <v>-3.802722598989182</v>
+        <v>-4.081049904492803</v>
       </c>
       <c r="G92">
-        <v>-3.704984948761526</v>
+        <v>-3.091934815253748</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.04497526315500785</v>
       </c>
       <c r="E93">
-        <v>-30.80278643178355</v>
+        <v>-31.29725050868108</v>
       </c>
       <c r="F93">
-        <v>-3.8951957372659</v>
+        <v>-4.550551152684103</v>
       </c>
       <c r="G93">
-        <v>-2.787050123814568</v>
+        <v>-3.662576860403462</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.03820511972820915</v>
       </c>
       <c r="E94">
-        <v>-32.30868970676826</v>
+        <v>-32.33538732528048</v>
       </c>
       <c r="F94">
-        <v>-4.126718627776542</v>
+        <v>-4.135467844284911</v>
       </c>
       <c r="G94">
-        <v>-3.535518122606234</v>
+        <v>-2.928794441624003</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.01789283498483235</v>
       </c>
       <c r="E95">
-        <v>-34.05151594912327</v>
+        <v>-34.49982355469761</v>
       </c>
       <c r="F95">
-        <v>-4.19866565017929</v>
+        <v>-4.220048297947754</v>
       </c>
       <c r="G95">
-        <v>-4.093166276514308</v>
+        <v>-3.442958579873751</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.118822882531095</v>
       </c>
       <c r="E96">
-        <v>-36.10535552208808</v>
+        <v>-35.94114626185893</v>
       </c>
       <c r="F96">
-        <v>-3.978900606583984</v>
+        <v>-4.932398704148174</v>
       </c>
       <c r="G96">
-        <v>-4.267334077335366</v>
+        <v>-3.778939225563305</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.2548815874609561</v>
       </c>
       <c r="E97">
-        <v>-38.4953708914863</v>
+        <v>-38.31323113842379</v>
       </c>
       <c r="F97">
-        <v>-4.308614855552869</v>
+        <v>-4.682395765248478</v>
       </c>
       <c r="G97">
-        <v>-5.009482244692562</v>
+        <v>-3.622234552461903</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4176023030089457</v>
       </c>
       <c r="E98">
-        <v>-40.48940517246881</v>
+        <v>-39.30171323752909</v>
       </c>
       <c r="F98">
-        <v>-4.52949405330494</v>
+        <v>-4.849888340624927</v>
       </c>
       <c r="G98">
-        <v>-5.178124745008576</v>
+        <v>-4.361876636845872</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5942607086829392</v>
       </c>
       <c r="E99">
-        <v>-42.74613849487327</v>
+        <v>-41.94876932007669</v>
       </c>
       <c r="F99">
-        <v>-4.999278603147999</v>
+        <v>-4.824485625850677</v>
       </c>
       <c r="G99">
-        <v>-5.186771889957152</v>
+        <v>-4.247527083373906</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7767224451369</v>
       </c>
       <c r="E100">
-        <v>-44.28718952086852</v>
+        <v>-44.84641530454974</v>
       </c>
       <c r="F100">
-        <v>-4.606115552961686</v>
+        <v>-5.470138373879891</v>
       </c>
       <c r="G100">
-        <v>-5.967696477215832</v>
+        <v>-5.325738660059138</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.9502234439299951</v>
       </c>
       <c r="E101">
-        <v>-45.93962515779342</v>
+        <v>-45.81625820463946</v>
       </c>
       <c r="F101">
-        <v>-4.804864915547968</v>
+        <v>-5.113203143687612</v>
       </c>
       <c r="G101">
-        <v>-5.502915746775393</v>
+        <v>-5.015825249945806</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.117733465212429</v>
       </c>
       <c r="E102">
-        <v>-47.2672763746512</v>
+        <v>-47.71507226266269</v>
       </c>
       <c r="F102">
-        <v>-5.402585840548994</v>
+        <v>-5.444103614777305</v>
       </c>
       <c r="G102">
-        <v>-6.136997776094161</v>
+        <v>-5.026584522948437</v>
       </c>
     </row>
   </sheetData>
